--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534561.9425649229</v>
+        <v>534562</v>
       </c>
       <c r="R2" t="n">
-        <v>6284383.725043911</v>
+        <v>6284384</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534663.4218192378</v>
+        <v>534663</v>
       </c>
       <c r="R3" t="n">
-        <v>6284285.197129902</v>
+        <v>6284285</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12086-2024 artfynd.xlsx
+++ b/artfynd/A 12086-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74412504</v>
       </c>
       <c r="B2" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74844767</v>
       </c>
       <c r="B3" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
